--- a/output/pdf_financials_xlsx/FRED.xlsx
+++ b/output/pdf_financials_xlsx/FRED.xlsx
@@ -5728,19 +5728,19 @@
         </is>
       </c>
       <c r="J92" s="3" t="n">
-        <v>1.008539</v>
+        <v>1.705363</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>1.023808</v>
+        <v>3.066747</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>1.221145</v>
+        <v>3.264084</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>1.221145</v>
+        <v>3.702556</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>1.714891</v>
+        <v>4.196302</v>
       </c>
     </row>
     <row r="93">
@@ -9358,7 +9358,11 @@
           <t>Warrants reserve (Note 6c)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -9907,7 +9911,11 @@
           <t>Warrants reserve (Note 6c)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10804,7 +10812,11 @@
           <t>Warrants reserve (Note 7c)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11373,7 +11385,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
